--- a/data-vh/Неделя_02.02-08.02_2026_ВХ.xlsx
+++ b/data-vh/Неделя_02.02-08.02_2026_ВХ.xlsx
@@ -2,39 +2,55 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="22320" windowHeight="13176" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Лист_1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Лист_1'!$A$1:$Q$31</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
+  <fonts count="3">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
+      <name val="Arial"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="8"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4ECC5"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -42,15 +58,149 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCC085"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCC085"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCC085"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCC085"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCC085"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -125,9 +275,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -165,7 +315,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -199,6 +349,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,9 +384,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -410,1885 +562,2081 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="10.42578125" defaultRowHeight="11.4" customHeight="1"/>
+  <cols>
+    <col width="5.140625" customWidth="1" style="1" min="1" max="1"/>
+    <col width="5.28515625" customWidth="1" style="1" min="2" max="2"/>
+    <col width="3.7109375" customWidth="1" style="1" min="3" max="3"/>
+    <col width="5" customWidth="1" style="1" min="4" max="4"/>
+    <col width="10.140625" customWidth="1" style="1" min="5" max="5"/>
+    <col width="22.5703125" customWidth="1" style="1" min="6" max="6"/>
+    <col width="21" customWidth="1" style="1" min="7" max="7"/>
+    <col width="29.7109375" customWidth="1" style="1" min="8" max="8"/>
+    <col width="18.5703125" customWidth="1" style="1" min="9" max="9"/>
+    <col width="32.140625" customWidth="1" style="1" min="10" max="10"/>
+    <col width="13.7109375" customWidth="1" style="1" min="11" max="11"/>
+    <col width="7.28515625" customWidth="1" style="1" min="12" max="12"/>
+    <col width="8.28515625" customWidth="1" style="1" min="13" max="13"/>
+    <col width="27.5703125" customWidth="1" style="1" min="14" max="14"/>
+    <col width="30.7109375" customWidth="1" style="1" min="15" max="15"/>
+    <col width="74.7109375" customWidth="1" style="1" min="16" max="16"/>
+    <col width="44.28515625" customWidth="1" style="1" min="17" max="17"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="25.95" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>№ п/п</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Номер</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="C1" s="21" t="n"/>
+      <c r="D1" s="22" t="n"/>
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>Дата</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="17" t="inlineStr">
         <is>
           <t>Основание</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="18" t="inlineStr">
         <is>
           <t>Поставщик/Переработчик</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Поставщик</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="I1" s="15" t="inlineStr">
         <is>
           <t>Место проведения контроля</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="15" t="inlineStr">
         <is>
           <t>Номенклатура</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="15" t="inlineStr">
         <is>
           <t>Группа номенклатуры</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="15" t="inlineStr">
         <is>
           <t>Кол., шт.</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="15" t="inlineStr">
         <is>
           <t>Кол., кг</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="15" t="inlineStr">
         <is>
           <t>Вид несоответствия</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="15" t="inlineStr">
         <is>
           <t>Критичность несоответствия</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="15" t="inlineStr">
         <is>
           <t>Несоответствие</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="15" t="inlineStr">
         <is>
           <t>Решение</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" ht="46.95" customHeight="1">
+      <c r="A2" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="C2" s="21" t="n"/>
+      <c r="D2" s="22" t="n"/>
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Поставщик</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="M2" s="13" t="n"/>
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>Пакет 11БПР756: Дефекты термической резки:    - чрезмерная/неравномерная глубина линий бороздок    Дефекты ЦП:    - забоины до основного металла    - несплошность ЦП в месте контакта с подвесочной проволокой    - наплывы, препятствующие сборке</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="Q2" s="7" t="n"/>
+    </row>
+    <row r="3" ht="46.95" customHeight="1">
+      <c r="A3" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="C3" s="21" t="n"/>
+      <c r="D3" s="22" t="n"/>
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Поставщик</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="M3" s="13" t="n"/>
+      <c r="N3" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="7" t="inlineStr">
         <is>
           <t>Пакет 12БПР604: Дефекты термической резки:    - чрезмерная/неравномерная глубина линий бороздок    Дефекты ЦП:    - забоины до основного металла    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="Q3" s="7" t="n"/>
+    </row>
+    <row r="4" ht="46.95" customHeight="1">
+      <c r="A4" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="C4" s="21" t="n"/>
+      <c r="D4" s="22" t="n"/>
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Поставщик</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="M4" s="13" t="n"/>
+      <c r="N4" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t>Пакет 501: Дефекты термической резки:    - чрезмерная/неравномерная глубина линий бороздок    Дефекты ЦП:    -  наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)    - наплывы в виде острых капель</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="Q4" s="7" t="n"/>
+    </row>
+    <row r="5" ht="46.95" customHeight="1">
+      <c r="A5" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="C5" s="21" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Поставщик</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="M5" s="13" t="n"/>
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>Пакет 502: Дефекты термической резки:    - чрезмерная/неравномерная глубина линий бороздок    Дефекты ЦП:    - забоины до основного металла    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)    - наплывы в виде острых капель</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="Q5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="46.95" customHeight="1">
+      <c r="A6" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="C6" s="21" t="n"/>
+      <c r="D6" s="22" t="n"/>
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Поставщик</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="M6" s="13" t="n"/>
+      <c r="N6" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" s="7" t="inlineStr">
         <is>
           <t>Пакет 503: Дефекты термической резки:    - чрезмерная/неравномерная глубина линий бороздок.    Дефекты ЦП:    - забоины до основного металла;    - наплывы в отверстиях и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки).</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="Q6" s="7" t="n"/>
+    </row>
+    <row r="7" ht="34.95" customHeight="1">
+      <c r="A7" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Поставщик</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="M7" s="13" t="n"/>
+      <c r="N7" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O7" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" s="7" t="inlineStr">
         <is>
           <t>Пакет 505: Дефекты ЦП:    - забоины до основного металла    - заплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)    Мех. повреждения</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="Q7" s="7" t="n"/>
+    </row>
+    <row r="8" ht="22.95" customHeight="1">
+      <c r="A8" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="C8" s="21" t="n"/>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Поставщик</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="M8" s="13" t="n"/>
+      <c r="N8" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" s="7" t="inlineStr">
         <is>
           <t>Пакет 01(А+Б+В+Г+Д): Дефекты ЦП:    -  наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="Q8" s="7" t="n"/>
+    </row>
+    <row r="9" ht="34.95" customHeight="1">
+      <c r="A9" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="C9" s="21" t="n"/>
+      <c r="D9" s="22" t="n"/>
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Поставщик</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="M9" s="13" t="n"/>
+      <c r="N9" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O9" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9" s="7" t="inlineStr">
         <is>
           <t>Пакет 02А: Дефекты ЦП:    -  Наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)    - наплывы, препятствующие сборке    - аплывы в виде острых капель</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="Q9" s="7" t="n"/>
+    </row>
+    <row r="10" ht="34.95" customHeight="1">
+      <c r="A10" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="C10" s="21" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Поставщик</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="M10" s="13" t="n"/>
+      <c r="N10" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O10" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" s="7" t="inlineStr">
         <is>
           <t>Пакет 03 (А+Б): Дефекты ЦП:    -  забоины до основного металла    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)    - наплывы в виде острых капель</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
+      <c r="Q10" s="7" t="n"/>
+    </row>
+    <row r="11" ht="34.95" customHeight="1">
+      <c r="A11" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="C11" s="21" t="n"/>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Поставщик</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="M11" s="13" t="n"/>
+      <c r="N11" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11" s="7" t="inlineStr">
         <is>
           <t>Пакет 04А: Дефекты ЦП:    -  забоины до основного металла    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)    - наплывы в виде острых капель</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
+      <c r="Q11" s="7" t="n"/>
+    </row>
+    <row r="12" ht="34.95" customHeight="1">
+      <c r="A12" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="C12" s="21" t="n"/>
+      <c r="D12" s="22" t="n"/>
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Поставщик</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="M12" s="13" t="n"/>
+      <c r="N12" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P12" s="7" t="inlineStr">
         <is>
           <t>Пакет 05 (А+Б+В): Дефекты ЦП:    -  забоины до основного металла    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)    - наплывы в виде острых капель</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
+      <c r="Q12" s="7" t="n"/>
+    </row>
+    <row r="13" ht="34.95" customHeight="1">
+      <c r="A13" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="C13" s="21" t="n"/>
+      <c r="D13" s="22" t="n"/>
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Поставщик</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L13" t="n">
+      <c r="L13" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="M13" s="13" t="n"/>
+      <c r="N13" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P13" s="7" t="inlineStr">
         <is>
           <t>Пакет 06А: Дефекты ЦП:    -  забоины до основного металла    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)    - наплывы в виде острых капель</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
+      <c r="Q13" s="7" t="n"/>
+    </row>
+    <row r="14" ht="34.95" customHeight="1">
+      <c r="A14" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="C14" s="21" t="n"/>
+      <c r="D14" s="22" t="n"/>
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Поставщик</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L14" t="n">
+      <c r="L14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="M14" s="13" t="n"/>
+      <c r="N14" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P14" s="7" t="inlineStr">
         <is>
           <t>Пакет 07А: Дефекты ЦП:    -  забоины до основного металла    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)    - наплывы в виде острых капель</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
+      <c r="Q14" s="7" t="n"/>
+    </row>
+    <row r="15" ht="34.95" customHeight="1">
+      <c r="A15" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="C15" s="21" t="n"/>
+      <c r="D15" s="22" t="n"/>
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Поставщик</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L15" t="n">
+      <c r="L15" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="M15" s="13" t="n"/>
+      <c r="N15" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O15" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P15" s="7" t="inlineStr">
         <is>
           <t>Пакет 08А: Дефекты ЦП:    -  забоины до основного металла    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)    - наплывы в виде острых капель</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
+      <c r="Q15" s="7" t="n"/>
+    </row>
+    <row r="16" ht="34.95" customHeight="1">
+      <c r="A16" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="C16" s="21" t="n"/>
+      <c r="D16" s="22" t="n"/>
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Поставщик</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L16" t="n">
+      <c r="L16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="M16" s="13" t="n"/>
+      <c r="N16" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O16" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P16" s="7" t="inlineStr">
         <is>
           <t>Пакет 09 (А+Б): Дефекты ЦП:    -  забоины до основного металла    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)    - наплывы в виде острых капель</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
+      <c r="Q16" s="7" t="n"/>
+    </row>
+    <row r="17" ht="34.95" customHeight="1">
+      <c r="A17" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="C17" s="21" t="n"/>
+      <c r="D17" s="22" t="n"/>
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Поставщик</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L17" t="n">
+      <c r="L17" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="M17" s="13" t="n"/>
+      <c r="N17" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O17" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P17" s="7" t="inlineStr">
         <is>
           <t>Пакет 10БПР31: Дефекты ЦП:    - забоины до основного металла    - несплошность ЦП в месте контакта с подвесочной проволокой    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
+      <c r="Q17" s="7" t="n"/>
+    </row>
+    <row r="18" ht="34.95" customHeight="1">
+      <c r="A18" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="C18" s="21" t="n"/>
+      <c r="D18" s="22" t="n"/>
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Поставщик</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="L18" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="M18" s="13" t="n"/>
+      <c r="N18" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O18" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P18" s="7" t="inlineStr">
         <is>
           <t>Пакет 13АПР600: Дефекты ЦП:    -  забоины до основного металла    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)    - наплывы в виде острых капель</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
+      <c r="Q18" s="7" t="n"/>
+    </row>
+    <row r="19" ht="34.95" customHeight="1">
+      <c r="A19" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="C19" s="21" t="n"/>
+      <c r="D19" s="22" t="n"/>
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Поставщик</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L19" t="n">
+      <c r="L19" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="M19" s="13" t="n"/>
+      <c r="N19" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O19" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P19" s="7" t="inlineStr">
         <is>
           <t>Пакет 13БПР600: Дефекты ЦП:    -  забоины до основного металла    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)    - наплывы в виде острых капель</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
+      <c r="Q19" s="7" t="n"/>
+    </row>
+    <row r="20" ht="34.95" customHeight="1">
+      <c r="A20" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="C20" s="21" t="n"/>
+      <c r="D20" s="22" t="n"/>
+      <c r="E20" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Поставщик</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L20" t="n">
+      <c r="L20" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="M20" s="13" t="n"/>
+      <c r="N20" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O20" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P20" s="7" t="inlineStr">
         <is>
           <t>Пакет 13ВПР600: Дефекты ЦП:    -  забоины до основного металла    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)    - наплывы в виде острых капель</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
+      <c r="Q20" s="7" t="n"/>
+    </row>
+    <row r="21" ht="22.95" customHeight="1">
+      <c r="A21" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="22" t="n"/>
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Поставщик</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K21" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L21" t="n">
+      <c r="L21" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="M21" s="13" t="n"/>
+      <c r="N21" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O21" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P21" s="7" t="inlineStr">
         <is>
           <t>Пакет 14А: Дефекты ЦП:    - забоины до основного металла</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
+      <c r="Q21" s="7" t="n"/>
+    </row>
+    <row r="22" ht="22.95" customHeight="1">
+      <c r="A22" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="C22" s="21" t="n"/>
+      <c r="D22" s="22" t="n"/>
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Поставщик</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K22" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L22" t="n">
+      <c r="L22" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="M22" s="13" t="n"/>
+      <c r="N22" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O22" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P22" s="7" t="inlineStr">
         <is>
           <t>Пакет 15А: Дефекты ЦП:    -  наплывы, препятствующие сборке</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
+      <c r="Q22" s="7" t="n"/>
+    </row>
+    <row r="23" ht="34.95" customHeight="1">
+      <c r="A23" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="C23" s="21" t="n"/>
+      <c r="D23" s="22" t="n"/>
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Поставщик</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K23" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L23" t="n">
+      <c r="L23" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="M23" s="13" t="n"/>
+      <c r="N23" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="O23" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P23" s="7" t="inlineStr">
         <is>
           <t>Пакет 500: Дефекты ЦП:    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)    - наплывы в виде острых капель</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
+      <c r="Q23" s="7" t="n"/>
+    </row>
+    <row r="24" ht="22.95" customHeight="1">
+      <c r="A24" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="22" t="n"/>
+      <c r="E24" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Поставщик</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K24" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L24" t="n">
+      <c r="L24" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="M24" s="13" t="n"/>
+      <c r="N24" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O24" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P24" s="7" t="inlineStr">
         <is>
           <t>Пакет 504: Дефекты ЦП:    - забоины до основного металла</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
+      <c r="Q24" s="7" t="n"/>
+    </row>
+    <row r="25" ht="22.95" customHeight="1">
+      <c r="A25" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="C25" s="21" t="n"/>
+      <c r="D25" s="22" t="n"/>
+      <c r="E25" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Поставщик</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K25" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L25" t="n">
+      <c r="L25" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="M25" s="13" t="n"/>
+      <c r="N25" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="O25" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P25" s="7" t="inlineStr">
         <is>
           <t>Пакет 506: Дефекты ЦП:    - забоины до основного металла    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
+      <c r="Q25" s="7" t="n"/>
+    </row>
+    <row r="26" ht="22.95" customHeight="1">
+      <c r="A26" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>В00-0000013</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="C26" s="21" t="n"/>
+      <c r="D26" s="22" t="n"/>
+      <c r="E26" s="16" t="inlineStr">
         <is>
           <t>02.02.2026</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Поставщик</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>Уральский завод металлоконструкций (6660000590 УМЕКОН АО)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>Корпус №01</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>(ПРЯМ.П) Опора ПП 500-7 с литьем (АО "УМЕКОН")</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K26" s="7" t="inlineStr">
         <is>
           <t>1.01.13 Прямая поставка (перепродажа) (товар 41 счет) АО Завод Продмаш</t>
         </is>
       </c>
-      <c r="L26" t="n">
+      <c r="L26" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="M26" s="13" t="n"/>
+      <c r="N26" s="7" t="inlineStr">
         <is>
           <t>Несоответствия ЦП</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O26" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P26" s="7" t="inlineStr">
         <is>
           <t>Пакет 507: Дефекты ЦП:    - забоины до основного металла    - наплыв в отверстии и на плоской поверхности, примыкающей к отверстию (от подвесочной проволоки)</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
+      <c r="Q26" s="7" t="n"/>
+    </row>
+    <row r="27" ht="46.95" customHeight="1">
+      <c r="A27" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>В00-0000014</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="C27" s="21" t="n"/>
+      <c r="D27" s="22" t="n"/>
+      <c r="E27" s="16" t="inlineStr">
         <is>
           <t>03.02.2026</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000057 от 03.02.2026 9:57:49</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>АСТРЕЯ ООО (ЭДО Такском ЗП согл. от 19.03.2025)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>Склад ПФ</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Ствол опоры ФГН-10,0-02 (ОО 270.01.00.000 СБ)  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K27" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L27" t="n">
+      <c r="L27" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M27" s="10" t="n">
         <v>1661.88</v>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N27" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O27" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P27" s="7" t="inlineStr">
         <is>
           <t>1. Брызги металла. 2. Сварной шов №4 выполнен с прерываниями по незамкнутому контуру. 3. Натёки. 4. Несплавление. 5. Подрезы. 6. Асимметрия сварного шва №4. 7. Межваликовый подрез. 8. По КД расстояние внутри лючка 98+0,5-1мм, фактически до 99.44мм.</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q27" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами сотрудников</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" ht="46.95" customHeight="1">
+      <c r="A28" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>В00-0000015</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="C28" s="21" t="n"/>
+      <c r="D28" s="22" t="n"/>
+      <c r="E28" s="16" t="inlineStr">
         <is>
           <t>04.02.2026</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>КЕДР-1 ООО (ЭДО ЗП с 21.01.2026)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>КЕДР-1 ООО (ЭДО ЗП с 21.01.2026)</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Настил Р 44,4х22,2/30х2 1 А 996х1000 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K28" s="7" t="inlineStr">
         <is>
           <t>Настилы прессованные</t>
         </is>
       </c>
-      <c r="L28" t="n">
+      <c r="L28" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M28" s="12" t="n">
         <v>3250</v>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N28" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O28" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P28" s="7" t="inlineStr">
         <is>
           <t>Прожог.     Брызги металла диаметром более 1,5 мм.     Соединение полос несущих и обрамления:     - несплавление (отсутствие соединения между основным и наплавленным металлом);     - неправильная форма сварного шва (отклонение от требуемой формы и геометрии).</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q28" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранить силами переработчика</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
+    <row r="29" ht="22.95" customHeight="1">
+      <c r="A29" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>В00-0000016</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="C29" s="21" t="n"/>
+      <c r="D29" s="22" t="n"/>
+      <c r="E29" s="16" t="inlineStr">
         <is>
           <t>05.02.2026</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-000624 от 04.02.2026 23:56:11</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Поставщик</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>ЕВРАЗ Маркет (ЕВРАЗ Металл Инпром) (ЭДО Такском)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>Основной склад</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>_уу_Труба 80*40*2,0 ГОСТ 8645-68/ Ст3сп, Ст3сп5 (С255, Ст2сп)</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K29" s="7" t="inlineStr">
         <is>
           <t>2.1.1.2.1.3 Труба прямоугольная ГОСТ 8645-68</t>
         </is>
       </c>
-      <c r="L29" t="n">
+      <c r="L29" s="9" t="n">
         <v>21.36</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M29" s="9" t="n">
         <v>21.36</v>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N29" s="7" t="inlineStr">
         <is>
           <t>Механическое повреждение</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O29" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P29" s="7" t="inlineStr">
         <is>
           <t>Вогнутость на стороне 80мм до 5,2мм, по ГОСТ 8639 допускается не более 1мм.</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q29" s="7" t="inlineStr">
         <is>
           <t>Взять в работу с доработкой</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="n">
+    <row r="30" ht="58.95" customHeight="1">
+      <c r="A30" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>В00-0000017</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="C30" s="21" t="n"/>
+      <c r="D30" s="22" t="n"/>
+      <c r="E30" s="16" t="inlineStr">
         <is>
           <t>06.02.2026</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР17 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K30" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L30" t="n">
+      <c r="L30" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M30" s="14" t="n">
         <v>6178.3</v>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N30" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O30" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P30" s="7" t="inlineStr">
         <is>
           <t>ОР 021.02.00.000СБ:    Соед. деталей 2 и 1 Т1 катет 8 - фактически катет 6-8 мм.     Дефекты сварных швов: подрезы, брызги металла, наплывы, поры, плохое повторное возбуждение дуги.     ОР 001.01.001:    Шероховатость поверхностей (отверстия, торцы) термической резки более Rz 80, в наличие дефекты термической резки: неравномерная глубина линий бороздок, выхватывание.</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q30" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами переработчиков</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="n">
+    <row r="31" ht="22.95" customHeight="1">
+      <c r="A31" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>В00-0000018</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="C31" s="21" t="n"/>
+      <c r="D31" s="22" t="n"/>
+      <c r="E31" s="16" t="inlineStr">
         <is>
           <t>06.02.2026</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-000193 от 21.01.2026 12:06:41</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Поставщик</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>СЕВЕРСТАЛЬ ДИСТРИБУЦИЯ АО (ЭДО Такском)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>Основной склад</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr">
         <is>
           <t>_уу_Г/к штрипс 2,9*468 (0+2)/S235JR</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K31" s="7" t="inlineStr">
         <is>
           <t>Штрипсы</t>
         </is>
       </c>
-      <c r="L31" t="n">
+      <c r="L31" s="12" t="n">
         <v>4497</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M31" s="12" t="n">
         <v>4497</v>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N31" s="7" t="inlineStr">
         <is>
           <t>Механическое повреждение</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O31" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу с доработкой;</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P31" s="7" t="inlineStr">
         <is>
           <t>Механическое повреждение</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q31" s="7" t="inlineStr">
         <is>
           <t>Взять в работу с доработкой</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:Q31">
+    <filterColumn colId="1" hiddenButton="0" showButton="0"/>
+    <filterColumn colId="2" hiddenButton="0" showButton="0"/>
+  </autoFilter>
+  <mergeCells count="31">
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0" footer="0"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" pageOrder="overThenDown"/>
 </worksheet>
 </file>